--- a/output/pdf_financials_xlsx/WGF.xlsx
+++ b/output/pdf_financials_xlsx/WGF.xlsx
@@ -6200,16 +6200,16 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.01029</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.011303</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.019935</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.012252</v>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
@@ -6407,16 +6407,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.198246</v>
+        <v>-0.208536</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.41637</v>
+        <v>0.405067</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.5041639999999999</v>
+        <v>-0.484229</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.007147</v>
+        <v>-0.019399</v>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
@@ -12902,7 +12902,11 @@
           <t>Prepaids and deposits 26,563</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -13766,7 +13770,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -14808,7 +14816,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
         <v>0.022943</v>
       </c>
@@ -16264,7 +16276,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="n">
         <v>-0.01029</v>
       </c>

--- a/output/pdf_financials_xlsx/WGF.xlsx
+++ b/output/pdf_financials_xlsx/WGF.xlsx
@@ -2625,10 +2625,10 @@
         <v>0.11532</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.001275</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.5694709999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2723,10 +2723,10 @@
         <v>0.11532</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.001275</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.5694709999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3311,10 +3311,10 @@
         <v>0.000566</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.002401</v>
+        <v>0.001126</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.5694709999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
